--- a/data_voor_swing/gebiedsdefinities/elz.xlsx
+++ b/data_voor_swing/gebiedsdefinities/elz.xlsx
@@ -1,57 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <workbookPr showObjects="all" updateLinks="userSet" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" xWindow="480" yWindow="75" windowWidth="18075" windowHeight="12525" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="elz" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" calcMode="auto" refMode="A1" iterateCount="100"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.000000"/>
-    <numFmt numFmtId="171" formatCode="0.0000000"/>
-    <numFmt numFmtId="172" formatCode="0.00000000"/>
-    <numFmt numFmtId="173" formatCode="0.000000000"/>
-    <numFmt numFmtId="174" formatCode="0.0000000000"/>
-    <numFmt numFmtId="175" formatCode="0.00000000000"/>
-    <numFmt numFmtId="176" formatCode="0.000000000000"/>
-    <numFmt numFmtId="177" formatCode="0.0000000000000"/>
-    <numFmt numFmtId="178" formatCode="0.00000000000000"/>
-    <numFmt numFmtId="179" formatCode="0.000000000000000"/>
-    <numFmt numFmtId="180" formatCode="0.0000000000000000"/>
-  </numFmts>
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,41 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -381,34 +420,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" s="0" outlineLevel="0">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>volgnr</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>gebiedscode</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>naam_kort</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>naam</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="0" outlineLevel="0">
-      <c r="A2" s="23">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sequence nr</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>geoitem code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>short name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -427,8 +470,8 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:4" s="0" outlineLevel="0">
-      <c r="A3" s="23">
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -447,8 +490,8 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:4" s="0" outlineLevel="0">
-      <c r="A4" s="23">
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -467,8 +510,8 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:4" s="0" outlineLevel="0">
-      <c r="A5" s="23">
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -487,8 +530,8 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:4" s="0" outlineLevel="0">
-      <c r="A6" s="23">
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -507,8 +550,8 @@
         </is>
       </c>
     </row>
-    <row r="7" spans="1:4" s="0" outlineLevel="0">
-      <c r="A7" s="23">
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -527,8 +570,8 @@
         </is>
       </c>
     </row>
-    <row r="8" spans="1:4" s="0" outlineLevel="0">
-      <c r="A8" s="23">
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,8 +590,8 @@
         </is>
       </c>
     </row>
-    <row r="9" spans="1:4" s="0" outlineLevel="0">
-      <c r="A9" s="23">
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -567,8 +610,8 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:4" s="0" outlineLevel="0">
-      <c r="A10" s="23">
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -587,8 +630,8 @@
         </is>
       </c>
     </row>
-    <row r="11" spans="1:4" s="0" outlineLevel="0">
-      <c r="A11" s="23">
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -607,8 +650,8 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:4" s="0" outlineLevel="0">
-      <c r="A12" s="23">
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -627,8 +670,8 @@
         </is>
       </c>
     </row>
-    <row r="13" spans="1:4" s="0" outlineLevel="0">
-      <c r="A13" s="23">
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -647,8 +690,8 @@
         </is>
       </c>
     </row>
-    <row r="14" spans="1:4" s="0" outlineLevel="0">
-      <c r="A14" s="23">
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -667,8 +710,8 @@
         </is>
       </c>
     </row>
-    <row r="15" spans="1:4" s="0" outlineLevel="0">
-      <c r="A15" s="23">
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -687,8 +730,8 @@
         </is>
       </c>
     </row>
-    <row r="16" spans="1:4" s="0" outlineLevel="0">
-      <c r="A16" s="23">
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -707,8 +750,8 @@
         </is>
       </c>
     </row>
-    <row r="17" spans="1:4" s="0" outlineLevel="0">
-      <c r="A17" s="23">
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -727,8 +770,8 @@
         </is>
       </c>
     </row>
-    <row r="18" spans="1:4" s="0" outlineLevel="0">
-      <c r="A18" s="23">
+    <row r="18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -747,8 +790,8 @@
         </is>
       </c>
     </row>
-    <row r="19" spans="1:4" s="0" outlineLevel="0">
-      <c r="A19" s="23">
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -767,8 +810,8 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:4" s="0" outlineLevel="0">
-      <c r="A20" s="23">
+    <row r="20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -787,8 +830,8 @@
         </is>
       </c>
     </row>
-    <row r="21" spans="1:4" s="0" outlineLevel="0">
-      <c r="A21" s="23">
+    <row r="21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -807,8 +850,8 @@
         </is>
       </c>
     </row>
-    <row r="22" spans="1:4" s="0" outlineLevel="0">
-      <c r="A22" s="23">
+    <row r="22">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -827,8 +870,8 @@
         </is>
       </c>
     </row>
-    <row r="23" spans="1:4" s="0" outlineLevel="0">
-      <c r="A23" s="23">
+    <row r="23">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -847,8 +890,8 @@
         </is>
       </c>
     </row>
-    <row r="24" spans="1:4" s="0" outlineLevel="0">
-      <c r="A24" s="23">
+    <row r="24">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -867,8 +910,8 @@
         </is>
       </c>
     </row>
-    <row r="25" spans="1:4" s="0" outlineLevel="0">
-      <c r="A25" s="23">
+    <row r="25">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -887,88 +930,88 @@
         </is>
       </c>
     </row>
-    <row r="26" spans="1:4" s="0" outlineLevel="0">
-      <c r="A26" s="23">
+    <row r="26">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>elz26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MidWestLim</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MidWestLim</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>elz39</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Midden WVL</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Midden WVL</t>
         </is>
       </c>
     </row>
-    <row r="27" spans="1:4" s="0" outlineLevel="0">
-      <c r="A27" s="23">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>elz25</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Middenkempen</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Middenkempen</t>
         </is>
       </c>
     </row>
-    <row r="28" spans="1:4" s="0" outlineLevel="0">
-      <c r="A28" s="23">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>elz30</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Middenkust</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Middenkust</t>
         </is>
       </c>
     </row>
-    <row r="29" spans="1:4" s="0" outlineLevel="0">
-      <c r="A29" s="23">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>elz26</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MidWestLim</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>MidWestLim</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="0" outlineLevel="0">
-      <c r="A30" s="23">
+    <row r="30">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -987,8 +1030,8 @@
         </is>
       </c>
     </row>
-    <row r="31" spans="1:4" s="0" outlineLevel="0">
-      <c r="A31" s="23">
+    <row r="31">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1007,8 +1050,8 @@
         </is>
       </c>
     </row>
-    <row r="32" spans="1:4" s="0" outlineLevel="0">
-      <c r="A32" s="23">
+    <row r="32">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1027,8 +1070,8 @@
         </is>
       </c>
     </row>
-    <row r="33" spans="1:4" s="0" outlineLevel="0">
-      <c r="A33" s="23">
+    <row r="33">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1047,8 +1090,8 @@
         </is>
       </c>
     </row>
-    <row r="34" spans="1:4" s="0" outlineLevel="0">
-      <c r="A34" s="23">
+    <row r="34">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1067,8 +1110,8 @@
         </is>
       </c>
     </row>
-    <row r="35" spans="1:4" s="0" outlineLevel="0">
-      <c r="A35" s="23">
+    <row r="35">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1087,8 +1130,8 @@
         </is>
       </c>
     </row>
-    <row r="36" spans="1:4" s="0" outlineLevel="0">
-      <c r="A36" s="23">
+    <row r="36">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1107,108 +1150,108 @@
         </is>
       </c>
     </row>
-    <row r="37" spans="1:4" s="0" outlineLevel="0">
-      <c r="A37" s="23">
+    <row r="37">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>elz40</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RITS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>elz36</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Regio Aalst</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Regio Aalst</t>
         </is>
       </c>
     </row>
-    <row r="38" spans="1:4" s="0" outlineLevel="0">
-      <c r="A38" s="23">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>elz37</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Regio Grimbergen</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Regio Grimbergen</t>
         </is>
       </c>
     </row>
-    <row r="39" spans="1:4" s="0" outlineLevel="0">
-      <c r="A39" s="23">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>elz24</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Regio Menen</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Regio Menen</t>
         </is>
       </c>
     </row>
-    <row r="40" spans="1:4" s="0" outlineLevel="0">
-      <c r="A40" s="23">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>elz50</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Regio Waregem</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Regio Waregem</t>
         </is>
       </c>
     </row>
-    <row r="41" spans="1:4" s="0" outlineLevel="0">
-      <c r="A41" s="23">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>elz40</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>RITS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>RITS</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" spans="1:4" s="0" outlineLevel="0">
-      <c r="A42" s="23">
+    <row r="42">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1227,8 +1270,8 @@
         </is>
       </c>
     </row>
-    <row r="43" spans="1:4" s="0" outlineLevel="0">
-      <c r="A43" s="23">
+    <row r="43">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1247,8 +1290,8 @@
         </is>
       </c>
     </row>
-    <row r="44" spans="1:4" s="0" outlineLevel="0">
-      <c r="A44" s="23">
+    <row r="44">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1267,8 +1310,8 @@
         </is>
       </c>
     </row>
-    <row r="45" spans="1:4" s="0" outlineLevel="0">
-      <c r="A45" s="23">
+    <row r="45">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1287,8 +1330,8 @@
         </is>
       </c>
     </row>
-    <row r="46" spans="1:4" s="0" outlineLevel="0">
-      <c r="A46" s="23">
+    <row r="46">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1307,68 +1350,68 @@
         </is>
       </c>
     </row>
-    <row r="47" spans="1:4" s="0" outlineLevel="0">
-      <c r="A47" s="23">
+    <row r="47">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>elz4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>WE40</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>WE40</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>elz29</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Waasland NO</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Waasland NO</t>
         </is>
       </c>
     </row>
-    <row r="48" spans="1:4" s="0" outlineLevel="0">
-      <c r="A48" s="23">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>elz57</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Waasland ZW</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Waasland ZW</t>
         </is>
       </c>
     </row>
-    <row r="49" spans="1:4" s="0" outlineLevel="0">
-      <c r="A49" s="23">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>elz4</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>WE40</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>WE40</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" spans="1:4" s="0" outlineLevel="0">
-      <c r="A50" s="23">
+    <row r="50">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -1387,8 +1430,8 @@
         </is>
       </c>
     </row>
-    <row r="51" spans="1:4" s="0" outlineLevel="0">
-      <c r="A51" s="23">
+    <row r="51">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -1407,8 +1450,8 @@
         </is>
       </c>
     </row>
-    <row r="52" spans="1:4" s="0" outlineLevel="0">
-      <c r="A52" s="23">
+    <row r="52">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -1427,8 +1470,8 @@
         </is>
       </c>
     </row>
-    <row r="53" spans="1:4" s="0" outlineLevel="0">
-      <c r="A53" s="23">
+    <row r="53">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -1447,68 +1490,68 @@
         </is>
       </c>
     </row>
-    <row r="54" spans="1:4" s="0" outlineLevel="0">
-      <c r="A54" s="23">
+    <row r="54">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>elz54</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ZOLim</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ZOLim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>elz55</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ZORA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ZORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>elz53</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Zennevallei</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Zennevallei</t>
         </is>
       </c>
     </row>
-    <row r="55" spans="1:4" s="0" outlineLevel="0">
-      <c r="A55" s="23">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>elz54</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ZOLim</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>ZOLim</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" spans="1:4" s="0" outlineLevel="0">
-      <c r="A56" s="23">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>elz55</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ZORA</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>ZORA</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" spans="1:4" s="0" outlineLevel="0">
-      <c r="A57" s="23">
+    <row r="57">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -1527,8 +1570,8 @@
         </is>
       </c>
     </row>
-    <row r="58" spans="1:4" s="0" outlineLevel="0">
-      <c r="A58" s="23">
+    <row r="58">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -1547,8 +1590,8 @@
         </is>
       </c>
     </row>
-    <row r="59" spans="1:4" s="0" outlineLevel="0">
-      <c r="A59" s="23">
+    <row r="59">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -1567,8 +1610,8 @@
         </is>
       </c>
     </row>
-    <row r="60" spans="1:4" s="0" outlineLevel="0">
-      <c r="A60" s="23">
+    <row r="60">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -1587,8 +1630,8 @@
         </is>
       </c>
     </row>
-    <row r="61" spans="1:4" s="0" outlineLevel="0">
-      <c r="A61" s="23">
+    <row r="61">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -1607,8 +1650,8 @@
         </is>
       </c>
     </row>
-    <row r="62" spans="1:4" s="0" outlineLevel="0">
-      <c r="A62" s="23">
+    <row r="62">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -1628,6 +1671,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>